--- a/eval-suite/cases/003_dwb_trade_wide_f/mapping.xlsx
+++ b/eval-suite/cases/003_dwb_trade_wide_f/mapping.xlsx
@@ -2,40 +2,387 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="24980" windowHeight="11800" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="实体级mapping" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="属性级mapping" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
+  <fonts count="22">
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF006100"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF9C0006"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF9C6500"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color theme="0"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="34">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2563EB"/>
+        <bgColor rgb="FF2563EB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -43,15 +390,329 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD0D0D0"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD0D0D0"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD0D0D0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD0D0D0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -404,7 +1065,6 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
@@ -414,283 +1074,140 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:M2"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="4"/>
+  <cols>
+    <col width="14" customWidth="1" min="3" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="40" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>源表schema</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>源表物理表名</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
+    <row r="1" ht="31" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>序号</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>分组</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>源表schema*</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>源表中文名</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>源表别名</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>目标表schema</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>源表物理表名*</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>源表别名*</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>目标表逻辑schema*</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>目标表中文名</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>目标表物理表名</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>目标表物理名称*</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>取数规则</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>关联&amp;限定条件</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>备注</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>数据库类型</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
         <is>
           <t>ods</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>订单明细</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
         <is>
           <t>ods_trade_order_di</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>订单明细</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>o</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>dws</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>交易宽表</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>dwb_trade_wide_f</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
+          <t>dwb_trade_wide_i</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
           <t>主表</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>dwrdim</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>dim_cust_d</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>客户维表</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>dws</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>交易宽表</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>dwb_trade_wide_f</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>o.cust_id = c.cust_id</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>dwrdim</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>dim_product_d</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>商品维表</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>p</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>dws</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>交易宽表</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>dwb_trade_wide_f</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>o.product_id = p.product_id</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>取最新有效行</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>ods</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>ods_payment_di</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>支付明细</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>pay</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>dws</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>交易宽表</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>dwb_trade_wide_f</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>o.order_id = pay.order_id</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>需收敛(多行)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>ods</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>ods_logistics_di</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>物流明细</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>log</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>dws</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>交易宽表</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>dwb_trade_wide_f</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>o.order_id = log.order_id</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>需收敛(多行)</t>
-        </is>
-      </c>
-    </row>
+    <row r="4" ht="31" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -702,82 +1219,96 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:O9"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
+  <cols>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="45" customWidth="1" min="18" max="18"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
+    <row r="1" ht="31" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>序号</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>分组</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>源Schema</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>源表物理表名</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>源表物理表别名</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>源表字段中文名</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>源表字段名</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>源表字段类型</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>映射规则*</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>映射表达式</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>目标字段名*</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>目标字段中文名</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>目标字段类型</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>数据标准</t>
+        </is>
+      </c>
     </row>
-    <row r="2">
+    <row r="2" ht="31" customHeight="1">
       <c r="A2" t="n">
         <v>1</v>
       </c>
@@ -846,8 +1377,9 @@
           <t>主键</t>
         </is>
       </c>
+      <c r="O2" t="inlineStr"/>
     </row>
-    <row r="3">
+    <row r="3" ht="31" customHeight="1">
       <c r="A3" t="n">
         <v>2</v>
       </c>
@@ -912,8 +1444,9 @@
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
     </row>
-    <row r="4">
+    <row r="4" ht="46" customHeight="1">
       <c r="A4" t="n">
         <v>3</v>
       </c>
@@ -978,8 +1511,9 @@
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
     </row>
-    <row r="5">
+    <row r="5" ht="76" customHeight="1">
       <c r="A5" t="n">
         <v>4</v>
       </c>
@@ -1044,8 +1578,9 @@
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
     </row>
-    <row r="6">
+    <row r="6" ht="122" customHeight="1">
       <c r="A6" t="n">
         <v>5</v>
       </c>
@@ -1069,49 +1604,42 @@
           <t>o</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>订单数量</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>order_qty</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>DECIMAL(18,4)</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>直接复制</t>
+          <t>赋值</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>'N'</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>order_qty</t>
+          <t>del_flag</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>订单数量</t>
+          <t>删除标识</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>DECIMAL(18,4)</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>NVARCHAR(1)</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>审计字段</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
     </row>
-    <row r="7">
+    <row r="7" ht="122" customHeight="1">
       <c r="A7" t="n">
         <v>6</v>
       </c>
@@ -1122,62 +1650,55 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>dwrdim</t>
+          <t>ods</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>dim_cust_d</t>
+          <t>ods_trade_order_di</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>客户名称</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>cust_name</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>VARCHAR(200)</t>
-        </is>
-      </c>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>直接复制</t>
+          <t>赋值</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>'${P_CYCLE_ID}'</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>cust_name</t>
+          <t>crt_cycle_id</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>客户名称</t>
+          <t>创建批次</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>VARCHAR(200)</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+          <t>BIGINT</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>审计字段</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr"/>
     </row>
-    <row r="8">
+    <row r="8" ht="122" customHeight="1">
       <c r="A8" t="n">
         <v>7</v>
       </c>
@@ -1188,62 +1709,55 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>dwrdim</t>
+          <t>ods</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>dim_cust_d</t>
+          <t>ods_trade_order_di</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>客户等级</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>cust_level</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>VARCHAR(10)</t>
-        </is>
-      </c>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>直接复制</t>
+          <t>赋值</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>'${P_CYCLE_ID}'</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>cust_level</t>
+          <t>last_upd_cycle_id</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>客户等级</t>
+          <t>更新批次</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>VARCHAR(10)</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
+          <t>BIGINT</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>审计字段</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr"/>
     </row>
-    <row r="9">
+    <row r="9" ht="122" customHeight="1">
       <c r="A9" t="n">
         <v>8</v>
       </c>
@@ -1254,443 +1768,58 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>dwrdim</t>
+          <t>ods</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>dim_product_d</t>
+          <t>ods_trade_order_di</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>p</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>商品名称</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>product_name</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>VARCHAR(200)</t>
-        </is>
-      </c>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>直接复制</t>
+          <t>赋值</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>CURRENT_TIMESTAMP</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>product_name</t>
+          <t>dw_last_update_date</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>商品名称</t>
+          <t>更新时间</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>VARCHAR(200)</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
+          <t>TIMESTAMP(0)</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>审计字段</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr"/>
     </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>default</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>dwrdim</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>dim_product_d</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>p</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>商品分类</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>category_code</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>VARCHAR(50)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>直接复制</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>category_code</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>商品分类</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>VARCHAR(50)</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>default</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>ods</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>ods_payment_di</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>pay</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>支付金额</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>pay_amt</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>DECIMAL(18,2)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>数据加工</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>按订单汇总支付金额</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>total_pay_amt</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>支付总额</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>DECIMAL(18,2)</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>default</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>ods</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>ods_logistics_di</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>log</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>运费</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>ship_fee</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>DECIMAL(18,2)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>数据加工</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>按订单汇总运费</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>total_ship_fee</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>运费总额</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>DECIMAL(18,2)</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>default</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>赋值</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>'N'</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>del_flag</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>删除标识</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>NVARCHAR(1)</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>审计字段</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>default</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>赋值</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>'${P_CYCLE_ID}'</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>crt_cycle_id</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>创建批次</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>BIGINT</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>审计字段</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>default</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>赋值</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>'${P_CYCLE_ID}'</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>last_upd_cycle_id</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>更新批次</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>BIGINT</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>审计字段</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>default</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>赋值</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>CURRENT_TIMESTAMP</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>dw_last_update_date</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>更新时间</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>TIMESTAMP(0)</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>审计字段</t>
-        </is>
-      </c>
-    </row>
+    <row r="10" ht="46" customHeight="1"/>
+    <row r="11" ht="137" customHeight="1"/>
+    <row r="12" ht="152" customHeight="1"/>
+    <row r="13" ht="76" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/eval-suite/cases/003_dwb_trade_wide_f/mapping.xlsx
+++ b/eval-suite/cases/003_dwb_trade_wide_f/mapping.xlsx
@@ -1198,14 +1198,11 @@
           <t>dwb_trade_wide_i</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
           <t>主表</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
     </row>
     <row r="4" ht="31" customHeight="1"/>
   </sheetData>
@@ -1254,7 +1251,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>源表物理表别名</t>
+          <t>源表别名</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -1377,7 +1374,6 @@
           <t>主键</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr"/>
     </row>
     <row r="3" ht="31" customHeight="1">
       <c r="A3" t="n">
@@ -1443,8 +1439,6 @@
           <t>VARCHAR(64)</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
     </row>
     <row r="4" ht="46" customHeight="1">
       <c r="A4" t="n">
@@ -1510,8 +1504,6 @@
           <t>VARCHAR(64)</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
     </row>
     <row r="5" ht="76" customHeight="1">
       <c r="A5" t="n">
@@ -1577,8 +1569,6 @@
           <t>DECIMAL(18,2)</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
     </row>
     <row r="6" ht="122" customHeight="1">
       <c r="A6" t="n">
@@ -1604,9 +1594,6 @@
           <t>o</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>赋值</t>
@@ -1637,7 +1624,6 @@
           <t>审计字段</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr"/>
     </row>
     <row r="7" ht="122" customHeight="1">
       <c r="A7" t="n">
@@ -1663,9 +1649,6 @@
           <t>o</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>赋值</t>
@@ -1696,7 +1679,6 @@
           <t>审计字段</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr"/>
     </row>
     <row r="8" ht="122" customHeight="1">
       <c r="A8" t="n">
@@ -1722,9 +1704,6 @@
           <t>o</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>赋值</t>
@@ -1755,7 +1734,6 @@
           <t>审计字段</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr"/>
     </row>
     <row r="9" ht="122" customHeight="1">
       <c r="A9" t="n">
@@ -1781,9 +1759,6 @@
           <t>o</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>赋值</t>
@@ -1814,7 +1789,6 @@
           <t>审计字段</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr"/>
     </row>
     <row r="10" ht="46" customHeight="1"/>
     <row r="11" ht="137" customHeight="1"/>
